--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -969,7 +969,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>82.7%</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1413,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -1495,22 +1495,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -1577,22 +1577,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1659,22 +1659,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -1741,22 +1741,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -2331,49 +2331,45 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>23/11/2025</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>1/27</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -3602,49 +3598,45 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>23/11/2025</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4808,49 +4800,45 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>23/11/2025</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>21/27</t>
-        </is>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6014,49 +6002,45 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>23/11/2025</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>14/30</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7220,49 +7204,45 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>23/11/2025</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>12/23</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +965,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>80.3%</t>
         </is>
       </c>
     </row>
@@ -1819,22 +1819,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -1901,22 +1901,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1983,22 +1983,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -2065,22 +2065,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -2143,22 +2143,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -2221,22 +2221,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -8339,49 +8339,45 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E158" s="5" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H158" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I158" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9592,49 +9588,45 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H185" s="5" t="inlineStr">
-        <is>
-          <t>23/30</t>
-        </is>
-      </c>
-      <c r="I185" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10845,49 +10837,45 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H212" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I212" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12098,49 +12086,45 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="inlineStr">
-        <is>
-          <t>17/28</t>
-        </is>
-      </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13347,49 +13331,45 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H266" s="5" t="inlineStr">
-        <is>
-          <t>2/26</t>
-        </is>
-      </c>
-      <c r="I266" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14600,49 +14580,45 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="2" t="inlineStr">
         <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H293" s="5" t="inlineStr">
-        <is>
-          <t>1/29</t>
-        </is>
-      </c>
-      <c r="I293" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +965,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -1819,22 +1819,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>85.1%</t>
         </is>
       </c>
     </row>
@@ -1901,22 +1901,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -1983,22 +1983,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -2065,22 +2065,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -2143,22 +2143,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>78.0%</t>
         </is>
       </c>
     </row>
@@ -2221,22 +2221,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -8382,49 +8382,45 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>26/11/2025</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="inlineStr">
-        <is>
-          <t>1/23</t>
-        </is>
-      </c>
-      <c r="I159" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9631,49 +9627,45 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>26/11/2025</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H186" s="5" t="inlineStr">
-        <is>
-          <t>2/30</t>
-        </is>
-      </c>
-      <c r="I186" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10880,49 +10872,45 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>26/11/2025</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I213" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12129,49 +12117,45 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>26/11/2025</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H240" s="5" t="inlineStr">
-        <is>
-          <t>17/28</t>
-        </is>
-      </c>
-      <c r="I240" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13374,49 +13358,45 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>26/11/2025</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H267" s="5" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="I267" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14623,49 +14603,45 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C294" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E294" s="5" t="inlineStr">
+      <c r="E294" s="2" t="inlineStr">
         <is>
           <t>26/11/2025</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H294" s="5" t="inlineStr">
-        <is>
-          <t>20/29</t>
-        </is>
-      </c>
-      <c r="I294" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +965,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -1819,22 +1819,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>85.4%</t>
         </is>
       </c>
     </row>
@@ -1901,22 +1901,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -1983,22 +1983,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -2143,22 +2143,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -2221,22 +2221,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -8425,49 +8425,45 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E160" s="5" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>27/11/2025</t>
         </is>
       </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H160" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I160" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9670,49 +9666,45 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>27/11/2025</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H187" s="5" t="inlineStr">
-        <is>
-          <t>23/30</t>
-        </is>
-      </c>
-      <c r="I187" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10915,49 +10907,45 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>27/11/2025</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H214" s="5" t="inlineStr">
-        <is>
-          <t>3/26</t>
-        </is>
-      </c>
-      <c r="I214" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13401,49 +13389,45 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>27/11/2025</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H268" s="5" t="inlineStr">
-        <is>
-          <t>15/26</t>
-        </is>
-      </c>
-      <c r="I268" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14646,49 +14630,45 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E295" s="5" t="inlineStr">
+      <c r="E295" s="2" t="inlineStr">
         <is>
           <t>27/11/2025</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H295" s="5" t="inlineStr">
-        <is>
-          <t>15/29</t>
-        </is>
-      </c>
-      <c r="I295" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr"/>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -693,49 +693,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>29/11/2025</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -799,7 +795,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +850,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +961,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>73.6%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1323,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -1409,22 +1405,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>85.6%</t>
         </is>
       </c>
     </row>
@@ -1491,22 +1487,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -1573,22 +1569,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>83.4%</t>
         </is>
       </c>
     </row>
@@ -1655,22 +1651,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -1737,22 +1733,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -2433,49 +2429,45 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>29/11/2025</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -3676,49 +3668,45 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>29/11/2025</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>25/26</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4874,49 +4862,45 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>29/11/2025</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6072,49 +6056,45 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>29/11/2025</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7270,49 +7250,45 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E135" s="5" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>29/11/2025</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>23/23</t>
-        </is>
-      </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -744,49 +744,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>30/11/2025</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -795,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
@@ -850,7 +846,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -961,7 +957,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -1323,22 +1319,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -1405,22 +1401,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>85.4%</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1483,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -1569,22 +1565,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1647,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>83.9%</t>
         </is>
       </c>
     </row>
@@ -1733,22 +1729,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -2487,49 +2483,45 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>30/11/2025</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -3711,49 +3703,45 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>30/11/2025</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4905,49 +4893,45 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>30/11/2025</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6099,49 +6083,45 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>30/11/2025</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H110" s="5" t="inlineStr">
-        <is>
-          <t>23/30</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7293,49 +7273,45 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>30/11/2025</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,53 +791,49 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>01/12/2025</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -846,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -957,7 +953,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>69.8%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1010,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
@@ -1319,22 +1315,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.9%</t>
         </is>
       </c>
     </row>
@@ -1401,22 +1397,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.8%</t>
         </is>
       </c>
     </row>
@@ -1483,22 +1479,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -1565,22 +1561,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>83.4%</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1643,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>83.7%</t>
         </is>
       </c>
     </row>
@@ -1729,22 +1725,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -2541,49 +2537,45 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>01/12/2025</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>21/27</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -3746,49 +3738,45 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>01/12/2025</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4936,49 +4924,45 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>01/12/2025</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6126,49 +6110,45 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>01/12/2025</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7316,49 +7296,45 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E137" s="5" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>01/12/2025</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr">
-        <is>
-          <t>15/23</t>
-        </is>
-      </c>
-      <c r="I137" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -953,7 +953,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -1807,22 +1807,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.1%</t>
         </is>
       </c>
     </row>
@@ -1889,22 +1889,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -1971,22 +1971,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -2053,22 +2053,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -2131,22 +2131,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
@@ -8396,49 +8396,45 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E161" s="5" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>02/12/2025</t>
         </is>
       </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="inlineStr">
-        <is>
-          <t>21/23</t>
-        </is>
-      </c>
-      <c r="I161" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9637,49 +9633,45 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>02/12/2025</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H188" s="5" t="inlineStr">
-        <is>
-          <t>23/30</t>
-        </is>
-      </c>
-      <c r="I188" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10878,49 +10870,45 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>02/12/2025</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H215" s="5" t="inlineStr">
-        <is>
-          <t>24/26</t>
-        </is>
-      </c>
-      <c r="I215" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12119,49 +12107,45 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>02/12/2025</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H242" s="5" t="inlineStr">
-        <is>
-          <t>18/28</t>
-        </is>
-      </c>
-      <c r="I242" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13360,49 +13344,45 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>02/12/2025</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H269" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I269" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14601,49 +14581,45 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="2" t="inlineStr">
         <is>
           <t>02/12/2025</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H296" s="5" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I296" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr"/>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
@@ -953,7 +953,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -1807,22 +1807,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>85.5%</t>
         </is>
       </c>
     </row>
@@ -1889,22 +1889,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
     </row>
@@ -1971,22 +1971,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -2053,22 +2053,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -2131,22 +2131,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>78.8%</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -8439,49 +8439,45 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E162" s="5" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H162" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9676,49 +9672,45 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H189" s="5" t="inlineStr">
-        <is>
-          <t>27/30</t>
-        </is>
-      </c>
-      <c r="I189" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10913,49 +10905,45 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H216" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I216" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12150,49 +12138,45 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H243" s="5" t="inlineStr">
-        <is>
-          <t>14/28</t>
-        </is>
-      </c>
-      <c r="I243" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13387,49 +13371,45 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H270" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I270" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14624,49 +14604,45 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E297" s="2" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H297" s="5" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I297" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr"/>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -953,7 +953,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -1807,22 +1807,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -1889,22 +1889,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>83.7%</t>
         </is>
       </c>
     </row>
@@ -1971,22 +1971,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -2053,22 +2053,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -2131,22 +2131,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -8482,49 +8482,45 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E163" s="5" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>04/12/2025</t>
         </is>
       </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>22/23</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9715,49 +9711,45 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>04/12/2025</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H190" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I190" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10948,49 +10940,45 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>04/12/2025</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H217" s="5" t="inlineStr">
-        <is>
-          <t>24/26</t>
-        </is>
-      </c>
-      <c r="I217" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12181,49 +12169,45 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>04/12/2025</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H244" s="5" t="inlineStr">
-        <is>
-          <t>21/28</t>
-        </is>
-      </c>
-      <c r="I244" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13414,49 +13398,45 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>04/12/2025</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H271" s="5" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="I271" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14647,49 +14627,45 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E298" s="5" t="inlineStr">
+      <c r="E298" s="2" t="inlineStr">
         <is>
           <t>04/12/2025</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H298" s="5" t="inlineStr">
-        <is>
-          <t>15/29</t>
-        </is>
-      </c>
-      <c r="I298" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr"/>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -842,53 +842,49 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>06/12/2025</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -953,7 +949,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1006,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
@@ -1315,22 +1311,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -1397,22 +1393,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.4%</t>
         </is>
       </c>
     </row>
@@ -1479,22 +1475,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -1561,22 +1557,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>83.1%</t>
         </is>
       </c>
     </row>
@@ -1643,22 +1639,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -1725,22 +1721,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -2595,49 +2591,45 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>06/12/2025</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3781,49 +3773,45 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>06/12/2025</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>25/26</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4967,49 +4955,45 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>06/12/2025</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6153,49 +6137,45 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>06/12/2025</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H112" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7339,49 +7319,45 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>06/12/2025</t>
         </is>
       </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G138" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H138" s="5" t="inlineStr">
-        <is>
-          <t>21/23</t>
-        </is>
-      </c>
-      <c r="I138" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
@@ -897,49 +897,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>07/12/2025</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -949,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>60.4%</t>
         </is>
       </c>
     </row>
@@ -1311,17 +1307,17 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -1393,22 +1389,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.2%</t>
         </is>
       </c>
     </row>
@@ -1475,17 +1471,17 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -1557,22 +1553,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>83.2%</t>
         </is>
       </c>
     </row>
@@ -1639,22 +1635,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>83.1%</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1717,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.0%</t>
         </is>
       </c>
     </row>
@@ -2634,49 +2630,45 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>07/12/2025</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3816,49 +3808,45 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>07/12/2025</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4998,49 +4986,45 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>07/12/2025</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6180,49 +6164,45 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>07/12/2025</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>27/30</t>
-        </is>
-      </c>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7362,49 +7342,45 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>07/12/2025</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>16/23</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
@@ -945,54 +945,50 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1002,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -1307,22 +1303,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -1389,17 +1385,17 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -1471,22 +1467,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -1553,22 +1549,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>84.1%</t>
         </is>
       </c>
     </row>
@@ -1635,17 +1631,17 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -1717,17 +1713,17 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
@@ -2673,49 +2669,45 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3851,49 +3843,45 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5029,49 +5017,45 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6207,49 +6191,45 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>25/30</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7385,49 +7365,45 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>19/23</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -1795,22 +1795,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -1877,22 +1877,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -2041,22 +2041,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -2119,22 +2119,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -2197,22 +2197,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8453,49 +8453,45 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="5" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C164" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E164" s="5" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F164" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G164" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H164" s="5" t="inlineStr">
-        <is>
-          <t>22/23</t>
-        </is>
-      </c>
-      <c r="I164" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9682,49 +9678,45 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E191" s="5" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H191" s="5" t="inlineStr">
-        <is>
-          <t>23/30</t>
-        </is>
-      </c>
-      <c r="I191" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10911,49 +10903,45 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B218" s="5" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C218" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D218" s="5" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E218" s="5" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F218" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G218" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H218" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I218" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12140,49 +12128,45 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B245" s="5" t="inlineStr">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C245" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D245" s="5" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E245" s="5" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F245" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G245" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H245" s="5" t="inlineStr">
-        <is>
-          <t>26/28</t>
-        </is>
-      </c>
-      <c r="I245" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13369,49 +13353,45 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B272" s="5" t="inlineStr">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C272" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D272" s="5" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E272" s="5" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F272" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G272" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H272" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I272" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14598,49 +14578,45 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B299" s="5" t="inlineStr">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C299" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D299" s="5" t="inlineStr">
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E299" s="5" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F299" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G299" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H299" s="5" t="inlineStr">
-        <is>
-          <t>20/29</t>
-        </is>
-      </c>
-      <c r="I299" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -1795,22 +1795,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.8%</t>
         </is>
       </c>
     </row>
@@ -1877,22 +1877,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.4%</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -2041,22 +2041,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>79.8%</t>
         </is>
       </c>
     </row>
@@ -2119,22 +2119,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -2197,22 +2197,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>74.9%</t>
         </is>
       </c>
     </row>
@@ -8496,49 +8496,45 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C165" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D165" s="5" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E165" s="5" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G165" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="inlineStr">
-        <is>
-          <t>14/23</t>
-        </is>
-      </c>
-      <c r="I165" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9721,49 +9717,45 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B192" s="5" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C192" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D192" s="5" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E192" s="5" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F192" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G192" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H192" s="5" t="inlineStr">
-        <is>
-          <t>24/30</t>
-        </is>
-      </c>
-      <c r="I192" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10946,49 +10938,45 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B219" s="5" t="inlineStr">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C219" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D219" s="5" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E219" s="5" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F219" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H219" s="5" t="inlineStr">
-        <is>
-          <t>24/26</t>
-        </is>
-      </c>
-      <c r="I219" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12171,49 +12159,45 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B246" s="5" t="inlineStr">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C246" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D246" s="5" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E246" s="5" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F246" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G246" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H246" s="5" t="inlineStr">
-        <is>
-          <t>16/28</t>
-        </is>
-      </c>
-      <c r="I246" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13396,49 +13380,45 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B273" s="5" t="inlineStr">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C273" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D273" s="5" t="inlineStr">
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E273" s="5" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F273" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G273" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H273" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I273" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14621,49 +14601,45 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B300" s="5" t="inlineStr">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C300" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D300" s="5" t="inlineStr">
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E300" s="5" t="inlineStr">
+      <c r="E300" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F300" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G300" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H300" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I300" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr"/>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -1795,22 +1795,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -1877,22 +1877,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.8%</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -2041,22 +2041,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -2119,22 +2119,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -2197,22 +2197,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -8539,49 +8539,45 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B166" s="5" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C166" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D166" s="5" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E166" s="5" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>11/12/2025</t>
         </is>
       </c>
-      <c r="F166" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G166" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H166" s="5" t="inlineStr">
-        <is>
-          <t>20/23</t>
-        </is>
-      </c>
-      <c r="I166" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9760,49 +9756,45 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="inlineStr">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C193" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D193" s="5" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E193" s="5" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>11/12/2025</t>
         </is>
       </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G193" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H193" s="5" t="inlineStr">
-        <is>
-          <t>24/30</t>
-        </is>
-      </c>
-      <c r="I193" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10981,49 +10973,45 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B220" s="5" t="inlineStr">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C220" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D220" s="5" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E220" s="5" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>11/12/2025</t>
         </is>
       </c>
-      <c r="F220" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H220" s="5" t="inlineStr">
-        <is>
-          <t>25/26</t>
-        </is>
-      </c>
-      <c r="I220" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12202,49 +12190,45 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B247" s="5" t="inlineStr">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C247" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D247" s="5" t="inlineStr">
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E247" s="5" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>11/12/2025</t>
         </is>
       </c>
-      <c r="F247" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G247" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H247" s="5" t="inlineStr">
-        <is>
-          <t>19/28</t>
-        </is>
-      </c>
-      <c r="I247" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13423,49 +13407,45 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B274" s="5" t="inlineStr">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C274" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D274" s="5" t="inlineStr">
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E274" s="5" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>11/12/2025</t>
         </is>
       </c>
-      <c r="F274" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G274" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H274" s="5" t="inlineStr">
-        <is>
-          <t>17/26</t>
-        </is>
-      </c>
-      <c r="I274" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14644,49 +14624,45 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B301" s="5" t="inlineStr">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C301" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D301" s="5" t="inlineStr">
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E301" s="5" t="inlineStr">
+      <c r="E301" s="2" t="inlineStr">
         <is>
           <t>11/12/2025</t>
         </is>
       </c>
-      <c r="F301" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G301" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H301" s="5" t="inlineStr">
-        <is>
-          <t>14/29</t>
-        </is>
-      </c>
-      <c r="I301" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr"/>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.9%</t>
         </is>
       </c>
     </row>
@@ -1003,49 +1003,45 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>24/26</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1303,22 +1299,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1385,22 +1381,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>85.5%</t>
         </is>
       </c>
     </row>
@@ -1467,22 +1463,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -1549,22 +1545,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -1631,22 +1627,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -1713,22 +1709,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -2712,49 +2708,45 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3886,49 +3878,45 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>16/26</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5060,49 +5048,45 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6234,49 +6218,45 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I115" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7408,49 +7388,45 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr">
-        <is>
-          <t>20/23</t>
-        </is>
-      </c>
-      <c r="I141" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>49.1%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.9%</t>
         </is>
       </c>
     </row>
@@ -1046,49 +1046,45 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>14/12/2025</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1299,22 +1295,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1377,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -1463,22 +1459,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>78.5%</t>
         </is>
       </c>
     </row>
@@ -1545,22 +1541,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -1627,22 +1623,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -1709,22 +1705,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.2%</t>
         </is>
       </c>
     </row>
@@ -2751,49 +2747,45 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>14/12/2025</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3921,49 +3913,45 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>14/12/2025</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>17/26</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5091,49 +5079,45 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>14/12/2025</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6261,49 +6245,45 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>14/12/2025</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>24/30</t>
-        </is>
-      </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7431,49 +7411,45 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>14/12/2025</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="inlineStr">
-        <is>
-          <t>17/23</t>
-        </is>
-      </c>
-      <c r="I142" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>81.7%</t>
         </is>
       </c>
     </row>
@@ -1787,22 +1787,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P21" s="4" t="n">
         <v>14</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -1869,22 +1869,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P22" s="4" t="n">
         <v>14</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -1951,22 +1951,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P23" s="4" t="n">
         <v>14</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>79.6%</t>
         </is>
       </c>
     </row>
@@ -2033,22 +2033,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P24" s="4" t="n">
         <v>14</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -2111,22 +2111,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P25" s="4" t="n">
         <v>14</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -2189,22 +2189,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P26" s="4" t="n">
         <v>14</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -8534,49 +8534,45 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E167" s="5" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G167" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr">
-        <is>
-          <t>22/23</t>
-        </is>
-      </c>
-      <c r="I167" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9751,49 +9747,45 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B194" s="5" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C194" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D194" s="5" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E194" s="5" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F194" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G194" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H194" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I194" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10968,49 +10960,45 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B221" s="5" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C221" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D221" s="5" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E221" s="5" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F221" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G221" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H221" s="5" t="inlineStr">
-        <is>
-          <t>25/26</t>
-        </is>
-      </c>
-      <c r="I221" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12185,49 +12173,45 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B248" s="5" t="inlineStr">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C248" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D248" s="5" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E248" s="5" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F248" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G248" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H248" s="5" t="inlineStr">
-        <is>
-          <t>23/28</t>
-        </is>
-      </c>
-      <c r="I248" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13402,49 +13386,45 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B275" s="5" t="inlineStr">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C275" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="inlineStr">
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E275" s="5" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F275" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G275" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H275" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I275" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14619,49 +14599,45 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B302" s="5" t="inlineStr">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C302" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D302" s="5" t="inlineStr">
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E302" s="5" t="inlineStr">
+      <c r="E302" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F302" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G302" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H302" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I302" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr"/>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>81.9%</t>
         </is>
       </c>
     </row>
@@ -1787,22 +1787,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>85.1%</t>
         </is>
       </c>
     </row>
@@ -1869,22 +1869,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -1951,22 +1951,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -2033,22 +2033,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>79.8%</t>
         </is>
       </c>
     </row>
@@ -2111,22 +2111,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -2189,22 +2189,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -8577,49 +8577,45 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B168" s="5" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E168" s="5" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H168" s="5" t="inlineStr">
-        <is>
-          <t>19/23</t>
-        </is>
-      </c>
-      <c r="I168" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9790,49 +9786,45 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C195" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D195" s="5" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E195" s="5" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H195" s="5" t="inlineStr">
-        <is>
-          <t>24/30</t>
-        </is>
-      </c>
-      <c r="I195" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11003,49 +10995,45 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B222" s="5" t="inlineStr">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C222" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D222" s="5" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E222" s="5" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F222" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G222" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H222" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I222" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12216,49 +12204,45 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B249" s="5" t="inlineStr">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C249" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D249" s="5" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E249" s="5" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G249" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H249" s="5" t="inlineStr">
-        <is>
-          <t>25/28</t>
-        </is>
-      </c>
-      <c r="I249" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13429,49 +13413,45 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B276" s="5" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C276" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D276" s="5" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E276" s="5" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F276" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G276" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H276" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I276" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14642,49 +14622,45 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C303" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="5" t="inlineStr">
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E303" s="5" t="inlineStr">
+      <c r="E303" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F303" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H303" s="5" t="inlineStr">
-        <is>
-          <t>18/29</t>
-        </is>
-      </c>
-      <c r="I303" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr"/>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -1787,22 +1787,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>85.4%</t>
         </is>
       </c>
     </row>
@@ -1869,22 +1869,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>84.5%</t>
         </is>
       </c>
     </row>
@@ -1951,22 +1951,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -2033,22 +2033,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -2111,22 +2111,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -2189,22 +2189,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -8620,49 +8620,45 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>18/12/2025</t>
         </is>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="inlineStr">
-        <is>
-          <t>19/23</t>
-        </is>
-      </c>
-      <c r="I169" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9829,49 +9825,45 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E196" s="5" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>18/12/2025</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H196" s="5" t="inlineStr">
-        <is>
-          <t>27/30</t>
-        </is>
-      </c>
-      <c r="I196" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11038,49 +11030,45 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C223" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="5" t="inlineStr">
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E223" s="5" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>18/12/2025</t>
         </is>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H223" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I223" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12247,49 +12235,45 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="5" t="inlineStr">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E250" s="5" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>18/12/2025</t>
         </is>
       </c>
-      <c r="F250" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H250" s="5" t="inlineStr">
-        <is>
-          <t>21/28</t>
-        </is>
-      </c>
-      <c r="I250" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13456,49 +13440,45 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="5" t="inlineStr">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C277" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="inlineStr">
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E277" s="5" t="inlineStr">
+      <c r="E277" s="2" t="inlineStr">
         <is>
           <t>18/12/2025</t>
         </is>
       </c>
-      <c r="F277" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H277" s="5" t="inlineStr">
-        <is>
-          <t>23/26</t>
-        </is>
-      </c>
-      <c r="I277" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14665,49 +14645,45 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="inlineStr">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C304" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="5" t="inlineStr">
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E304" s="5" t="inlineStr">
+      <c r="E304" s="2" t="inlineStr">
         <is>
           <t>18/12/2025</t>
         </is>
       </c>
-      <c r="F304" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H304" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I304" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr"/>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -1089,49 +1089,45 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>20/12/2025</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>24/26</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1295,22 +1291,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -1377,22 +1373,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -1459,22 +1455,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>78.7%</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1537,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -1623,22 +1619,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1701,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -2790,49 +2786,45 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>20/12/2025</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3956,49 +3948,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>20/12/2025</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5122,49 +5110,45 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>20/12/2025</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6288,49 +6272,45 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>20/12/2025</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7454,49 +7434,45 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>20/12/2025</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>20/23</t>
-        </is>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -1137,49 +1137,45 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>25/26</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
@@ -1291,22 +1287,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1369,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.0%</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1451,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -1537,22 +1533,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>82.2%</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1615,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>83.0%</t>
         </is>
       </c>
     </row>
@@ -1701,22 +1697,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2829,49 +2825,45 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3991,49 +3983,45 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5153,49 +5141,45 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6315,49 +6299,45 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H118" s="5" t="inlineStr">
-        <is>
-          <t>28/30</t>
-        </is>
-      </c>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7477,49 +7457,45 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>23/23</t>
-        </is>
-      </c>
-      <c r="I144" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>37.7%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -1225,49 +1225,45 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1287,22 +1283,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1365,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>82.3%</t>
         </is>
       </c>
     </row>
@@ -1451,22 +1447,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1529,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>82.7%</t>
         </is>
       </c>
     </row>
@@ -1615,22 +1611,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -1697,22 +1693,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -2868,49 +2864,45 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4026,49 +4018,45 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5184,49 +5172,45 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>21/27</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6342,49 +6326,45 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>29/30</t>
-        </is>
-      </c>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7500,49 +7480,45 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E145" s="5" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I145" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1775,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>87.0%</t>
         </is>
       </c>
     </row>
@@ -1857,22 +1857,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.7%</t>
         </is>
       </c>
     </row>
@@ -1939,22 +1939,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>78.5%</t>
         </is>
       </c>
     </row>
@@ -2021,22 +2021,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -2099,17 +2099,17 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
@@ -2177,22 +2177,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -8591,49 +8591,45 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B170" s="5" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C170" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D170" s="5" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E170" s="5" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G170" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H170" s="5" t="inlineStr">
-        <is>
-          <t>16/23</t>
-        </is>
-      </c>
-      <c r="I170" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9796,49 +9792,45 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B197" s="5" t="inlineStr">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C197" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D197" s="5" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E197" s="5" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H197" s="5" t="inlineStr">
-        <is>
-          <t>25/30</t>
-        </is>
-      </c>
-      <c r="I197" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11001,49 +10993,45 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B224" s="5" t="inlineStr">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C224" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D224" s="5" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E224" s="5" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H224" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I224" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12206,49 +12194,45 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B251" s="5" t="inlineStr">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C251" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D251" s="5" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E251" s="5" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F251" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G251" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H251" s="5" t="inlineStr">
-        <is>
-          <t>21/28</t>
-        </is>
-      </c>
-      <c r="I251" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13411,49 +13395,45 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B278" s="5" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C278" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D278" s="5" t="inlineStr">
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E278" s="5" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F278" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G278" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H278" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I278" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14616,49 +14596,45 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B305" s="5" t="inlineStr">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C305" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D305" s="5" t="inlineStr">
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E305" s="5" t="inlineStr">
+      <c r="E305" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F305" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G305" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H305" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I305" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr"/>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>34.0%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -1857,22 +1857,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>85.9%</t>
         </is>
       </c>
     </row>
@@ -1939,22 +1939,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -2021,22 +2021,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>81.7%</t>
         </is>
       </c>
     </row>
@@ -2099,22 +2099,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -2177,22 +2177,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -8634,49 +8634,45 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E171" s="5" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G171" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>20/23</t>
-        </is>
-      </c>
-      <c r="I171" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9835,49 +9831,45 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B198" s="5" t="inlineStr">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C198" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D198" s="5" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E198" s="5" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F198" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G198" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H198" s="5" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I198" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11036,49 +11028,45 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B225" s="5" t="inlineStr">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C225" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D225" s="5" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E225" s="5" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F225" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G225" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H225" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I225" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12237,49 +12225,45 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B252" s="5" t="inlineStr">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C252" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D252" s="5" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E252" s="5" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F252" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G252" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H252" s="5" t="inlineStr">
-        <is>
-          <t>20/28</t>
-        </is>
-      </c>
-      <c r="I252" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13438,49 +13422,45 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B279" s="5" t="inlineStr">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C279" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D279" s="5" t="inlineStr">
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E279" s="5" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F279" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G279" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H279" s="5" t="inlineStr">
-        <is>
-          <t>15/26</t>
-        </is>
-      </c>
-      <c r="I279" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr"/>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14639,49 +14619,45 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B306" s="5" t="inlineStr">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C306" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D306" s="5" t="inlineStr">
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E306" s="5" t="inlineStr">
+      <c r="E306" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F306" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G306" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H306" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I306" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr"/>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1775,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -1857,22 +1857,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>85.8%</t>
         </is>
       </c>
     </row>
@@ -1939,22 +1939,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.8%</t>
         </is>
       </c>
     </row>
@@ -2021,22 +2021,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -2099,22 +2099,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>82.7%</t>
         </is>
       </c>
     </row>
@@ -2177,22 +2177,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>81.9%</t>
         </is>
       </c>
     </row>
@@ -8677,49 +8677,45 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="5" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E172" s="5" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>25/12/2025</t>
         </is>
       </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G172" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H172" s="5" t="inlineStr">
-        <is>
-          <t>19/23</t>
-        </is>
-      </c>
-      <c r="I172" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9874,49 +9870,45 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="inlineStr">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C199" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D199" s="5" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E199" s="5" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>25/12/2025</t>
         </is>
       </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H199" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I199" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11071,49 +11063,45 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B226" s="5" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C226" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D226" s="5" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E226" s="5" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>25/12/2025</t>
         </is>
       </c>
-      <c r="F226" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G226" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H226" s="5" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="I226" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12268,49 +12256,45 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B253" s="5" t="inlineStr">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C253" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E253" s="5" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>25/12/2025</t>
         </is>
       </c>
-      <c r="F253" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G253" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H253" s="5" t="inlineStr">
-        <is>
-          <t>21/28</t>
-        </is>
-      </c>
-      <c r="I253" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13465,49 +13449,45 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B280" s="5" t="inlineStr">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C280" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D280" s="5" t="inlineStr">
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E280" s="5" t="inlineStr">
+      <c r="E280" s="2" t="inlineStr">
         <is>
           <t>25/12/2025</t>
         </is>
       </c>
-      <c r="F280" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G280" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H280" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I280" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14662,49 +14642,45 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B307" s="5" t="inlineStr">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C307" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D307" s="5" t="inlineStr">
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E307" s="5" t="inlineStr">
+      <c r="E307" s="2" t="inlineStr">
         <is>
           <t>25/12/2025</t>
         </is>
       </c>
-      <c r="F307" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G307" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H307" s="5" t="inlineStr">
-        <is>
-          <t>16/29</t>
-        </is>
-      </c>
-      <c r="I307" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr"/>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>30.2%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.9%</t>
         </is>
       </c>
     </row>
@@ -1283,69 +1283,65 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1365,22 +1361,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1443,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1525,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1611,22 +1607,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -1693,22 +1689,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -2907,49 +2903,45 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4061,49 +4053,45 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5215,49 +5203,45 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>21/27</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6369,49 +6353,45 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7523,49 +7503,45 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E146" s="5" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1283,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -1361,17 +1361,17 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -1381,49 +1381,45 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1443,22 +1439,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>79.1%</t>
         </is>
       </c>
     </row>
@@ -1525,22 +1521,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -1607,22 +1603,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>81.9%</t>
         </is>
       </c>
     </row>
@@ -1689,22 +1685,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -2946,49 +2942,45 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4096,49 +4088,45 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5246,49 +5234,45 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6396,49 +6380,45 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7546,49 +7526,45 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G147" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr">
-        <is>
-          <t>21/23</t>
-        </is>
-      </c>
-      <c r="I147" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.2%</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1283,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -1361,22 +1361,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1439,69 +1439,65 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1521,22 +1517,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1599,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1681,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -2985,49 +2981,45 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4131,49 +4123,45 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5277,49 +5265,45 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>20/27</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6423,49 +6407,45 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7569,49 +7549,45 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E148" s="5" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I148" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -1763,22 +1763,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.8%</t>
         </is>
       </c>
     </row>
@@ -1845,22 +1845,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.2%</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.2%</t>
         </is>
       </c>
     </row>
@@ -2087,22 +2087,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>84.1%</t>
         </is>
       </c>
     </row>
@@ -2165,22 +2165,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -8648,49 +8648,45 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E173" s="5" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G173" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H173" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I173" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9841,49 +9837,45 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B200" s="5" t="inlineStr">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C200" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D200" s="5" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E200" s="5" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F200" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G200" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H200" s="5" t="inlineStr">
-        <is>
-          <t>27/30</t>
-        </is>
-      </c>
-      <c r="I200" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11034,49 +11026,45 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B227" s="5" t="inlineStr">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C227" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D227" s="5" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E227" s="5" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F227" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G227" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H227" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I227" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12227,49 +12215,45 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B254" s="5" t="inlineStr">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C254" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D254" s="5" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E254" s="5" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F254" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G254" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H254" s="5" t="inlineStr">
-        <is>
-          <t>22/28</t>
-        </is>
-      </c>
-      <c r="I254" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13420,49 +13404,45 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B281" s="5" t="inlineStr">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C281" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D281" s="5" t="inlineStr">
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E281" s="5" t="inlineStr">
+      <c r="E281" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F281" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G281" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H281" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I281" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr"/>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14613,49 +14593,45 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B308" s="5" t="inlineStr">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C308" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D308" s="5" t="inlineStr">
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E308" s="5" t="inlineStr">
+      <c r="E308" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F308" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G308" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H308" s="5" t="inlineStr">
-        <is>
-          <t>19/29</t>
-        </is>
-      </c>
-      <c r="I308" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr"/>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>82.8%</t>
         </is>
       </c>
     </row>
@@ -1763,22 +1763,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
     </row>
@@ -1845,22 +1845,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>87.8%</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>82.7%</t>
         </is>
       </c>
     </row>
@@ -2087,22 +2087,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
     </row>
@@ -2165,22 +2165,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
     </row>
@@ -8691,49 +8691,45 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B174" s="5" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D174" s="5" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E174" s="5" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G174" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H174" s="5" t="inlineStr">
-        <is>
-          <t>19/23</t>
-        </is>
-      </c>
-      <c r="I174" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9880,49 +9876,45 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C201" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D201" s="5" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E201" s="5" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H201" s="5" t="inlineStr">
-        <is>
-          <t>21/30</t>
-        </is>
-      </c>
-      <c r="I201" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11069,49 +11061,45 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B228" s="5" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C228" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D228" s="5" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E228" s="5" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F228" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G228" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H228" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I228" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12258,49 +12246,45 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B255" s="5" t="inlineStr">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C255" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E255" s="5" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G255" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H255" s="5" t="inlineStr">
-        <is>
-          <t>24/28</t>
-        </is>
-      </c>
-      <c r="I255" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13447,49 +13431,45 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B282" s="5" t="inlineStr">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C282" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D282" s="5" t="inlineStr">
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E282" s="5" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F282" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G282" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H282" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I282" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14636,49 +14616,45 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B309" s="5" t="inlineStr">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C309" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D309" s="5" t="inlineStr">
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E309" s="5" t="inlineStr">
+      <c r="E309" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F309" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G309" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H309" s="5" t="inlineStr">
-        <is>
-          <t>25/29</t>
-        </is>
-      </c>
-      <c r="I309" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr"/>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>82.2%</t>
         </is>
       </c>
     </row>
@@ -1763,22 +1763,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>88.7%</t>
         </is>
       </c>
     </row>
@@ -1845,22 +1845,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>87.3%</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -2087,22 +2087,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.4%</t>
         </is>
       </c>
     </row>
@@ -2165,22 +2165,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -8734,49 +8734,45 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E175" s="5" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G175" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H175" s="5" t="inlineStr">
-        <is>
-          <t>22/23</t>
-        </is>
-      </c>
-      <c r="I175" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9919,49 +9915,45 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B202" s="5" t="inlineStr">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C202" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E202" s="5" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="F202" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G202" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H202" s="5" t="inlineStr">
-        <is>
-          <t>27/30</t>
-        </is>
-      </c>
-      <c r="I202" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11104,49 +11096,45 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B229" s="5" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C229" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D229" s="5" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E229" s="5" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G229" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I229" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12289,49 +12277,45 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B256" s="5" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C256" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E256" s="5" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="F256" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G256" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H256" s="5" t="inlineStr">
-        <is>
-          <t>25/28</t>
-        </is>
-      </c>
-      <c r="I256" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13474,49 +13458,45 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B283" s="5" t="inlineStr">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C283" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D283" s="5" t="inlineStr">
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E283" s="5" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G283" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H283" s="5" t="inlineStr">
-        <is>
-          <t>22/26</t>
-        </is>
-      </c>
-      <c r="I283" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14659,49 +14639,45 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B310" s="5" t="inlineStr">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C310" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D310" s="5" t="inlineStr">
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E310" s="5" t="inlineStr">
+      <c r="E310" s="2" t="inlineStr">
         <is>
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="F310" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G310" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H310" s="5" t="inlineStr">
-        <is>
-          <t>28/29</t>
-        </is>
-      </c>
-      <c r="I310" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr"/>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>83.0%</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1283,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -1361,22 +1361,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1439,22 +1439,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -1517,69 +1517,65 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>78.7%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>19/26</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1599,17 +1595,17 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -1619,49 +1615,45 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1681,22 +1673,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -3024,96 +3016,88 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>20/27</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>20/27</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4166,96 +4150,88 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>17/26</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5308,96 +5284,88 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6450,96 +6418,88 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr">
-        <is>
-          <t>25/30</t>
-        </is>
-      </c>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="inlineStr">
-        <is>
-          <t>25/30</t>
-        </is>
-      </c>
-      <c r="I124" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7592,96 +7552,88 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr">
-        <is>
-          <t>17/23</t>
-        </is>
-      </c>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H150" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I150" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1283,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -1361,22 +1361,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -1439,22 +1439,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1517,22 +1517,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -1595,22 +1595,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -1673,69 +1673,65 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -3102,49 +3098,45 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4236,49 +4228,45 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5370,49 +5358,45 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6504,49 +6488,45 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E125" s="5" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7638,49 +7618,45 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E151" s="5" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr">
-        <is>
-          <t>23/23</t>
-        </is>
-      </c>
-      <c r="I151" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -1751,22 +1751,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>85.9%</t>
         </is>
       </c>
     </row>
@@ -1833,22 +1833,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -1915,22 +1915,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1997,22 +1997,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -2075,22 +2075,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>81.7%</t>
         </is>
       </c>
     </row>
@@ -2153,22 +2153,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -8705,49 +8705,45 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E176" s="5" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H176" s="5" t="inlineStr">
-        <is>
-          <t>23/23</t>
-        </is>
-      </c>
-      <c r="I176" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9886,49 +9882,45 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B203" s="5" t="inlineStr">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C203" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D203" s="5" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E203" s="5" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G203" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H203" s="5" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="I203" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11067,49 +11059,45 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B230" s="5" t="inlineStr">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C230" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D230" s="5" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E230" s="5" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G230" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H230" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I230" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12248,49 +12236,45 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B257" s="5" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C257" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D257" s="5" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E257" s="5" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G257" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H257" s="5" t="inlineStr">
-        <is>
-          <t>28/28</t>
-        </is>
-      </c>
-      <c r="I257" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13429,49 +13413,45 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B284" s="5" t="inlineStr">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C284" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D284" s="5" t="inlineStr">
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E284" s="5" t="inlineStr">
+      <c r="E284" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F284" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G284" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H284" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I284" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14610,49 +14590,45 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B311" s="5" t="inlineStr">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C311" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D311" s="5" t="inlineStr">
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E311" s="5" t="inlineStr">
+      <c r="E311" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F311" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G311" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H311" s="5" t="inlineStr">
-        <is>
-          <t>29/29</t>
-        </is>
-      </c>
-      <c r="I311" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr"/>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>74.5%</t>
         </is>
       </c>
     </row>
@@ -1751,22 +1751,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -1833,22 +1833,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -1915,22 +1915,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1997,22 +1997,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -2075,22 +2075,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>75.6%</t>
         </is>
       </c>
     </row>
@@ -2153,22 +2153,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -8748,49 +8748,45 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E177" s="5" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="inlineStr">
-        <is>
-          <t>23/23</t>
-        </is>
-      </c>
-      <c r="I177" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9925,49 +9921,45 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B204" s="5" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C204" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D204" s="5" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E204" s="5" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F204" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G204" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H204" s="5" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="I204" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11102,49 +11094,45 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B231" s="5" t="inlineStr">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C231" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D231" s="5" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E231" s="5" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H231" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I231" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12279,49 +12267,45 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B258" s="5" t="inlineStr">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C258" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D258" s="5" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E258" s="5" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F258" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G258" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H258" s="5" t="inlineStr">
-        <is>
-          <t>28/28</t>
-        </is>
-      </c>
-      <c r="I258" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13456,49 +13440,45 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B285" s="5" t="inlineStr">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C285" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D285" s="5" t="inlineStr">
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E285" s="5" t="inlineStr">
+      <c r="E285" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F285" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G285" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H285" s="5" t="inlineStr">
-        <is>
-          <t>26/26</t>
-        </is>
-      </c>
-      <c r="I285" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14633,49 +14613,45 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B312" s="5" t="inlineStr">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C312" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D312" s="5" t="inlineStr">
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E312" s="5" t="inlineStr">
+      <c r="E312" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F312" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G312" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H312" s="5" t="inlineStr">
-        <is>
-          <t>29/29</t>
-        </is>
-      </c>
-      <c r="I312" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr"/>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1751,22 +1751,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>84.8%</t>
         </is>
       </c>
     </row>
@@ -1833,22 +1833,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1915,22 +1915,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -1997,22 +1997,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -2075,22 +2075,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -2153,22 +2153,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -8791,49 +8791,45 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B178" s="5" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C178" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E178" s="5" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G178" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H178" s="5" t="inlineStr">
-        <is>
-          <t>17/23</t>
-        </is>
-      </c>
-      <c r="I178" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9964,49 +9960,45 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B205" s="5" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C205" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D205" s="5" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E205" s="5" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H205" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I205" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11137,49 +11129,45 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B232" s="5" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C232" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D232" s="5" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E232" s="5" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G232" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H232" s="5" t="inlineStr">
-        <is>
-          <t>14/26</t>
-        </is>
-      </c>
-      <c r="I232" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12310,49 +12298,45 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B259" s="5" t="inlineStr">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C259" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D259" s="5" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E259" s="5" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="F259" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G259" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H259" s="5" t="inlineStr">
-        <is>
-          <t>21/28</t>
-        </is>
-      </c>
-      <c r="I259" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13483,49 +13467,45 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B286" s="5" t="inlineStr">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C286" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D286" s="5" t="inlineStr">
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E286" s="5" t="inlineStr">
+      <c r="E286" s="2" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="F286" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G286" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H286" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I286" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14656,49 +14636,45 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B313" s="5" t="inlineStr">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C313" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D313" s="5" t="inlineStr">
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E313" s="5" t="inlineStr">
+      <c r="E313" s="2" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="F313" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G313" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H313" s="5" t="inlineStr">
-        <is>
-          <t>18/29</t>
-        </is>
-      </c>
-      <c r="I313" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr"/>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -1283,17 +1283,17 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -1361,22 +1361,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -1439,22 +1439,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -1517,22 +1517,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -1595,22 +1595,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -1673,22 +1673,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -1771,49 +1771,45 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -3141,49 +3137,45 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4271,49 +4263,45 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>23/26</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5401,49 +5389,45 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6531,49 +6515,45 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7661,49 +7641,45 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>18/23</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1283,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -1361,22 +1361,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -1439,17 +1439,17 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -1517,22 +1517,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
@@ -1595,22 +1595,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -1673,22 +1673,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -1849,49 +1849,45 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -3180,49 +3176,45 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4306,49 +4298,45 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5432,49 +5420,45 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>18/27</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6558,49 +6542,45 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr">
-        <is>
-          <t>23/30</t>
-        </is>
-      </c>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7684,49 +7664,45 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E153" s="5" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>16/23</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -93,9 +93,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -103,6 +100,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1283,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1361,22 +1361,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1439,22 +1439,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1517,22 +1517,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1595,22 +1595,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1673,22 +1673,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1927,49 +1927,45 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>16/26</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2403,7 +2399,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2461,7 +2457,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2519,7 +2515,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3219,49 +3215,45 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>17/27</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4341,49 +4333,45 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5463,49 +5451,45 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>16/27</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6585,49 +6569,45 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>21/30</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7707,49 +7687,45 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E154" s="5" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H154" s="5" t="inlineStr">
-        <is>
-          <t>17/23</t>
-        </is>
-      </c>
-      <c r="I154" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8786,94 +8762,94 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E179" s="5" t="inlineStr">
+      <c r="E179" s="8" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr">
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G179" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H179" s="5" t="inlineStr">
+      <c r="H179" s="8" t="inlineStr">
         <is>
           <t>20/23</t>
         </is>
       </c>
-      <c r="I179" s="5" t="inlineStr">
+      <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
+      <c r="A180" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C180" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E180" s="5" t="inlineStr">
+      <c r="E180" s="8" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F180" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G180" s="5" t="inlineStr">
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G180" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H180" s="5" t="inlineStr">
+      <c r="H180" s="8" t="inlineStr">
         <is>
           <t>19/23</t>
         </is>
       </c>
-      <c r="I180" s="5" t="inlineStr">
+      <c r="I180" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -9955,94 +9931,94 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B206" s="5" t="inlineStr">
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B206" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D206" s="5" t="inlineStr">
+      <c r="C206" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E206" s="5" t="inlineStr">
+      <c r="E206" s="8" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G206" s="5" t="inlineStr">
+      <c r="F206" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G206" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H206" s="5" t="inlineStr">
+      <c r="H206" s="8" t="inlineStr">
         <is>
           <t>23/30</t>
         </is>
       </c>
-      <c r="I206" s="5" t="inlineStr">
+      <c r="I206" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B207" s="5" t="inlineStr">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C207" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E207" s="5" t="inlineStr">
+      <c r="E207" s="8" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr">
+      <c r="F207" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G207" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H207" s="5" t="inlineStr">
+      <c r="H207" s="8" t="inlineStr">
         <is>
           <t>22/30</t>
         </is>
       </c>
-      <c r="I207" s="5" t="inlineStr">
+      <c r="I207" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -11124,94 +11100,94 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E233" s="5" t="inlineStr">
+      <c r="E233" s="8" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr">
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H233" s="5" t="inlineStr">
+      <c r="H233" s="8" t="inlineStr">
         <is>
           <t>21/26</t>
         </is>
       </c>
-      <c r="I233" s="5" t="inlineStr">
+      <c r="I233" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="inlineStr">
+      <c r="A234" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B234" s="8" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C234" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D234" s="5" t="inlineStr">
+      <c r="C234" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E234" s="5" t="inlineStr">
+      <c r="E234" s="8" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr">
+      <c r="F234" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G234" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H234" s="5" t="inlineStr">
+      <c r="H234" s="8" t="inlineStr">
         <is>
           <t>17/26</t>
         </is>
       </c>
-      <c r="I234" s="5" t="inlineStr">
+      <c r="I234" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -12293,94 +12269,94 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B260" s="5" t="inlineStr">
+      <c r="A260" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B260" s="8" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C260" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D260" s="5" t="inlineStr">
+      <c r="C260" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D260" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E260" s="5" t="inlineStr">
+      <c r="E260" s="8" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr">
+      <c r="F260" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G260" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H260" s="5" t="inlineStr">
+      <c r="H260" s="8" t="inlineStr">
         <is>
           <t>16/28</t>
         </is>
       </c>
-      <c r="I260" s="5" t="inlineStr">
+      <c r="I260" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C261" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D261" s="8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E261" s="5" t="inlineStr">
+      <c r="E261" s="8" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr">
+      <c r="F261" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G261" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H261" s="5" t="inlineStr">
+      <c r="H261" s="8" t="inlineStr">
         <is>
           <t>21/28</t>
         </is>
       </c>
-      <c r="I261" s="5" t="inlineStr">
+      <c r="I261" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -13462,94 +13438,94 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B287" s="5" t="inlineStr">
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C287" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D287" s="5" t="inlineStr">
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D287" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E287" s="5" t="inlineStr">
+      <c r="E287" s="8" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F287" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G287" s="5" t="inlineStr">
+      <c r="F287" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G287" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H287" s="5" t="inlineStr">
+      <c r="H287" s="8" t="inlineStr">
         <is>
           <t>18/26</t>
         </is>
       </c>
-      <c r="I287" s="5" t="inlineStr">
+      <c r="I287" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B288" s="5" t="inlineStr">
+      <c r="A288" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B288" s="8" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C288" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D288" s="5" t="inlineStr">
+      <c r="C288" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D288" s="8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E288" s="5" t="inlineStr">
+      <c r="E288" s="8" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F288" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G288" s="5" t="inlineStr">
+      <c r="F288" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G288" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H288" s="5" t="inlineStr">
+      <c r="H288" s="8" t="inlineStr">
         <is>
           <t>20/26</t>
         </is>
       </c>
-      <c r="I288" s="5" t="inlineStr">
+      <c r="I288" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -14631,94 +14607,94 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B314" s="5" t="inlineStr">
+      <c r="A314" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B314" s="8" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C314" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D314" s="5" t="inlineStr">
+      <c r="C314" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D314" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E314" s="5" t="inlineStr">
+      <c r="E314" s="8" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F314" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G314" s="5" t="inlineStr">
+      <c r="F314" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G314" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H314" s="5" t="inlineStr">
+      <c r="H314" s="8" t="inlineStr">
         <is>
           <t>21/29</t>
         </is>
       </c>
-      <c r="I314" s="5" t="inlineStr">
+      <c r="I314" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B315" s="5" t="inlineStr">
+      <c r="A315" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B315" s="8" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C315" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D315" s="5" t="inlineStr">
+      <c r="C315" s="8" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D315" s="8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E315" s="5" t="inlineStr">
+      <c r="E315" s="8" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F315" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G315" s="5" t="inlineStr">
+      <c r="F315" s="8" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G315" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H315" s="5" t="inlineStr">
+      <c r="H315" s="8" t="inlineStr">
         <is>
           <t>21/29</t>
         </is>
       </c>
-      <c r="I315" s="5" t="inlineStr">
+      <c r="I315" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
@@ -1751,22 +1751,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -1829,22 +1829,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -1907,22 +1907,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -1985,22 +1985,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2063,22 +2063,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -2141,17 +2141,17 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
@@ -8762,49 +8762,45 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C179" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D179" s="8" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E179" s="8" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F179" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G179" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H179" s="8" t="inlineStr">
-        <is>
-          <t>20/23</t>
-        </is>
-      </c>
-      <c r="I179" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9931,49 +9927,45 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B206" s="8" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C206" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D206" s="8" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E206" s="8" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F206" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G206" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H206" s="8" t="inlineStr">
-        <is>
-          <t>23/30</t>
-        </is>
-      </c>
-      <c r="I206" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11100,49 +11092,45 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B233" s="8" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C233" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D233" s="8" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E233" s="8" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F233" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H233" s="8" t="inlineStr">
-        <is>
-          <t>21/26</t>
-        </is>
-      </c>
-      <c r="I233" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12269,49 +12257,45 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B260" s="8" t="inlineStr">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C260" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D260" s="8" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E260" s="8" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F260" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G260" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H260" s="8" t="inlineStr">
-        <is>
-          <t>16/28</t>
-        </is>
-      </c>
-      <c r="I260" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13438,49 +13422,45 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B287" s="8" t="inlineStr">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C287" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D287" s="8" t="inlineStr">
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E287" s="8" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F287" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G287" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H287" s="8" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="I287" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14607,49 +14587,45 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B314" s="8" t="inlineStr">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C314" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D314" s="8" t="inlineStr">
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E314" s="8" t="inlineStr">
+      <c r="E314" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F314" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G314" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H314" s="8" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I314" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr"/>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -100,9 +100,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -791,7 +788,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +839,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +942,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -998,7 +995,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1751,22 +1748,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1829,22 +1826,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1907,22 +1904,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1985,22 +1982,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2063,22 +2060,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2141,22 +2138,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -8805,49 +8802,45 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C180" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D180" s="8" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E180" s="8" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F180" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G180" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H180" s="8" t="inlineStr">
-        <is>
-          <t>19/23</t>
-        </is>
-      </c>
-      <c r="I180" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>0/23</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9970,49 +9963,45 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B207" s="8" t="inlineStr">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C207" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D207" s="8" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E207" s="8" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F207" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G207" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H207" s="8" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I207" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11135,49 +11124,45 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B234" s="8" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>B1E1</t>
         </is>
       </c>
-      <c r="C234" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D234" s="8" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E234" s="8" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F234" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G234" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H234" s="8" t="inlineStr">
-        <is>
-          <t>17/26</t>
-        </is>
-      </c>
-      <c r="I234" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12300,49 +12285,45 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B261" s="8" t="inlineStr">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>B1E2</t>
         </is>
       </c>
-      <c r="C261" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D261" s="8" t="inlineStr">
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E261" s="8" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F261" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G261" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H261" s="8" t="inlineStr">
-        <is>
-          <t>21/28</t>
-        </is>
-      </c>
-      <c r="I261" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13465,49 +13446,45 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B288" s="8" t="inlineStr">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
         <is>
           <t>B1F1</t>
         </is>
       </c>
-      <c r="C288" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D288" s="8" t="inlineStr">
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E288" s="8" t="inlineStr">
+      <c r="E288" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F288" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G288" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H288" s="8" t="inlineStr">
-        <is>
-          <t>20/26</t>
-        </is>
-      </c>
-      <c r="I288" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>0/26</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14630,49 +14607,45 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B315" s="8" t="inlineStr">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
         <is>
           <t>B1F2</t>
         </is>
       </c>
-      <c r="C315" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D315" s="8" t="inlineStr">
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E315" s="8" t="inlineStr">
+      <c r="E315" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F315" s="8" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G315" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H315" s="8" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I315" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr"/>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
